--- a/trial_source/src/main/resources/static/template/Task.25_レビュー記録票_製造_未入力勤怠ダイアログ画面 .xlsx
+++ b/trial_source/src/main/resources/static/template/Task.25_レビュー記録票_製造_未入力勤怠ダイアログ画面 .xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASK_001\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASK_001\git\lms-src-rp1\trial_source\src\main\resources\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7AFA31-E30C-47FB-BC6A-341428C655C6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B505E52C-DBFC-4515-86B4-D3F02000892C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="1155" windowWidth="20010" windowHeight="10890" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="1155" windowWidth="20010" windowHeight="10890" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="レビュー前セルフチェック記録表_Task.●●" sheetId="1" r:id="rId1"/>
-    <sheet name="レビュー記録表_Task.●●" sheetId="2" r:id="rId2"/>
+    <sheet name="レビュー前セルフチェック記録表_Task.25" sheetId="1" r:id="rId1"/>
+    <sheet name="レビュー記録表_Task.25" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録表_Task.●●!$A$1:$BC$109</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー前セルフチェック記録表_Task.●●!$A$1:$BC$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録表_Task.25!$A$1:$BC$109</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー前セルフチェック記録表_Task.25!$A$1:$BC$35</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
   <si>
     <t>プロジェクト名</t>
   </si>
@@ -417,13 +417,6 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>書面</t>
-  </si>
-  <si>
-    <t>PL○○</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -466,6 +459,183 @@
   </si>
   <si>
     <t>NG</t>
+  </si>
+  <si>
+    <t>田中</t>
+    <rPh sb="0" eb="2">
+      <t>タナカ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>TStudentAttendanceMapper.xml</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TStudentAttendanceMapper.xml
+</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>コードの記述について</t>
+    <rPh sb="4" eb="6">
+      <t>キジュツ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>コードの内容に説明できない部分があった
+	AND &lt;![CDATA[
+        training_date &lt; ((#{trainingDate})::date)::timestamp
+        ]]&gt;</t>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブブン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>対面</t>
+    <rPh sb="0" eb="2">
+      <t>タイメン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>田中 将悟</t>
+    <rPh sb="0" eb="2">
+      <t>タナカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サトル</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>益子講師</t>
+    <rPh sb="0" eb="2">
+      <t>マシコ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>名前をどう付けたか聞かれた際に、自分で考えたといってしまった。（実際は仕様書通り)</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>説明の誤り</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>SQLの説明の際、0以上、1以上と言ってしまった。正しくは０より大きい場合。
+ニュアンスでいってしまったが記述が変わってしまうので要注意。</t>
+    <rPh sb="4" eb="6">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>ヨウチュウイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>改めてどういう仕様か確認し、記述の機能を確認する</t>
+    <rPh sb="0" eb="1">
+      <t>アラタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>記述自体は間違っていなかったが、仕様書の確認が甘かったので、きちんと確認する。</t>
+    <rPh sb="0" eb="2">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>TStudentAttendanceMapper.java
+notEnterCountメソッド</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>メソッドの名前について</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -829,6 +999,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -879,9 +1052,6 @@
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2347,200 +2517,200 @@
   <sheetData>
     <row r="1" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="14" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="14"/>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="15" t="s">
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="16" t="s">
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
+      <c r="AO2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AP2" s="16"/>
-      <c r="AQ2" s="16"/>
-      <c r="AR2" s="16"/>
-      <c r="AS2" s="16"/>
-      <c r="AT2" s="16" t="s">
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="17"/>
+      <c r="AS2" s="17"/>
+      <c r="AT2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AU2" s="16"/>
-      <c r="AV2" s="16"/>
-      <c r="AW2" s="16"/>
-      <c r="AX2" s="16"/>
-      <c r="AY2" s="17" t="s">
+      <c r="AU2" s="17"/>
+      <c r="AV2" s="17"/>
+      <c r="AW2" s="17"/>
+      <c r="AX2" s="17"/>
+      <c r="AY2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="AZ2" s="17"/>
-      <c r="BA2" s="17"/>
-      <c r="BB2" s="17"/>
-      <c r="BC2" s="17"/>
+      <c r="AZ2" s="18"/>
+      <c r="BA2" s="18"/>
+      <c r="BB2" s="18"/>
+      <c r="BC2" s="18"/>
     </row>
     <row r="3" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="19" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="20" t="str">
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="21" t="str">
         <f>" "&amp;S6</f>
         <v xml:space="preserve"> Task.25,未入力勤怠確認画面の新作成</v>
       </c>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK3" s="21"/>
-      <c r="AL3" s="21"/>
-      <c r="AM3" s="21"/>
-      <c r="AN3" s="21"/>
-      <c r="AO3" s="22">
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
+      <c r="AM3" s="22"/>
+      <c r="AN3" s="22"/>
+      <c r="AO3" s="23">
         <v>45922</v>
       </c>
-      <c r="AP3" s="22"/>
-      <c r="AQ3" s="22"/>
-      <c r="AR3" s="22"/>
-      <c r="AS3" s="22"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="24"/>
-      <c r="AZ3" s="24"/>
-      <c r="BA3" s="24"/>
-      <c r="BB3" s="24"/>
-      <c r="BC3" s="24"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
     </row>
     <row r="4" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="20"/>
-      <c r="AE4" s="20"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="20"/>
-      <c r="AH4" s="20"/>
-      <c r="AI4" s="20"/>
-      <c r="AJ4" s="21"/>
-      <c r="AK4" s="21"/>
-      <c r="AL4" s="21"/>
-      <c r="AM4" s="21"/>
-      <c r="AN4" s="21"/>
-      <c r="AO4" s="22"/>
-      <c r="AP4" s="22"/>
-      <c r="AQ4" s="22"/>
-      <c r="AR4" s="22"/>
-      <c r="AS4" s="22"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-      <c r="AY4" s="24"/>
-      <c r="AZ4" s="24"/>
-      <c r="BA4" s="24"/>
-      <c r="BB4" s="24"/>
-      <c r="BC4" s="24"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="21"/>
+      <c r="AG4" s="21"/>
+      <c r="AH4" s="21"/>
+      <c r="AI4" s="21"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
     </row>
     <row r="6" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
@@ -2549,36 +2719,36 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
       <c r="O6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
+      <c r="S6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
       <c r="AC6" s="6" t="s">
         <v>11</v>
       </c>
@@ -2587,11 +2757,11 @@
       <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
-      <c r="AI6" s="9"/>
-      <c r="AJ6" s="9"/>
-      <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="10"/>
+      <c r="AK6" s="10"/>
+      <c r="AL6" s="10"/>
+      <c r="AM6" s="10"/>
       <c r="AN6" s="6" t="s">
         <v>12</v>
       </c>
@@ -2600,41 +2770,41 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
       <c r="AS6" s="6"/>
-      <c r="AT6" s="10"/>
-      <c r="AU6" s="10"/>
-      <c r="AV6" s="10"/>
-      <c r="AW6" s="10"/>
-      <c r="AX6" s="10"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
     </row>
     <row r="7" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
       <c r="AC7" s="6" t="s">
         <v>13</v>
       </c>
@@ -2643,11 +2813,11 @@
       <c r="AF7" s="6"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
-      <c r="AI7" s="11"/>
-      <c r="AJ7" s="11"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
       <c r="AN7" s="6" t="s">
         <v>14</v>
       </c>
@@ -2656,41 +2826,41 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
       <c r="AS7" s="6"/>
-      <c r="AT7" s="11"/>
-      <c r="AU7" s="11"/>
-      <c r="AV7" s="11"/>
-      <c r="AW7" s="11"/>
-      <c r="AX7" s="11"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
     </row>
     <row r="8" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
       <c r="AC8" s="6" t="s">
         <v>15</v>
       </c>
@@ -2884,7 +3054,7 @@
       <c r="AH12" s="7"/>
       <c r="AI12" s="7"/>
       <c r="AJ12" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
@@ -2948,7 +3118,7 @@
       <c r="AH13" s="2"/>
       <c r="AI13" s="2"/>
       <c r="AJ13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
@@ -3012,7 +3182,7 @@
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
@@ -3076,7 +3246,7 @@
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
       <c r="AJ15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
@@ -3140,7 +3310,7 @@
       <c r="AH16" s="2"/>
       <c r="AI16" s="2"/>
       <c r="AJ16" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
@@ -3204,7 +3374,7 @@
       <c r="AH17" s="2"/>
       <c r="AI17" s="2"/>
       <c r="AJ17" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
@@ -3268,7 +3438,7 @@
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
       <c r="AJ18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
@@ -3332,7 +3502,7 @@
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
       <c r="AJ19" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
@@ -3396,7 +3566,7 @@
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
       <c r="AJ20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
@@ -3460,7 +3630,7 @@
       <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
       <c r="AJ21" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
@@ -3524,7 +3694,7 @@
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
       <c r="AJ22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
@@ -3588,7 +3758,7 @@
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
       <c r="AJ23" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
@@ -3652,7 +3822,7 @@
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
       <c r="AJ24" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
@@ -3834,7 +4004,7 @@
       <c r="AH27" s="2"/>
       <c r="AI27" s="2"/>
       <c r="AJ27" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
@@ -4076,7 +4246,7 @@
       <c r="AH31" s="2"/>
       <c r="AI31" s="2"/>
       <c r="AJ31" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
@@ -4140,7 +4310,7 @@
       <c r="AH32" s="2"/>
       <c r="AI32" s="2"/>
       <c r="AJ32" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
@@ -4203,7 +4373,7 @@
       <c r="AH33" s="2"/>
       <c r="AI33" s="2"/>
       <c r="AJ33" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
@@ -4267,7 +4437,7 @@
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
@@ -4709,27 +4879,27 @@
   <sheetData>
     <row r="1" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
       <c r="R2" s="28" t="s">
         <v>36</v>
       </c>
@@ -4750,34 +4920,34 @@
       <c r="AG2" s="28"/>
       <c r="AH2" s="28"/>
       <c r="AI2" s="28"/>
-      <c r="AJ2" s="15" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="16" t="s">
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
+      <c r="AO2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AP2" s="16"/>
-      <c r="AQ2" s="16"/>
-      <c r="AR2" s="16"/>
-      <c r="AS2" s="16"/>
-      <c r="AT2" s="16" t="s">
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="17"/>
+      <c r="AS2" s="17"/>
+      <c r="AT2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AU2" s="16"/>
-      <c r="AV2" s="16"/>
-      <c r="AW2" s="16"/>
-      <c r="AX2" s="16"/>
-      <c r="AY2" s="17" t="s">
+      <c r="AU2" s="17"/>
+      <c r="AV2" s="17"/>
+      <c r="AW2" s="17"/>
+      <c r="AX2" s="17"/>
+      <c r="AY2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="AZ2" s="17"/>
-      <c r="BA2" s="17"/>
-      <c r="BB2" s="17"/>
-      <c r="BC2" s="17"/>
+      <c r="AZ2" s="18"/>
+      <c r="BA2" s="18"/>
+      <c r="BB2" s="18"/>
+      <c r="BC2" s="18"/>
     </row>
     <row r="3" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="29" t="s">
@@ -4791,59 +4961,59 @@
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="20" t="str">
-        <f>E6&amp;S6</f>
-        <v>AttendanceController.java
-AttendanceServise.java
-AttendanceMapper.XMLTask.25,未入力勤怠確認画面の新作成</v>
-      </c>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="21"/>
-      <c r="AL3" s="21"/>
-      <c r="AM3" s="21"/>
-      <c r="AN3" s="21"/>
-      <c r="AO3" s="22"/>
-      <c r="AP3" s="22"/>
-      <c r="AQ3" s="22"/>
-      <c r="AR3" s="22"/>
-      <c r="AS3" s="22"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="24"/>
-      <c r="AZ3" s="24"/>
-      <c r="BA3" s="24"/>
-      <c r="BB3" s="24"/>
-      <c r="BC3" s="24"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="21" t="str">
+        <f>S6</f>
+        <v>Task.25,未入力勤怠確認画面の新作成</v>
+      </c>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
+      <c r="AM3" s="22"/>
+      <c r="AN3" s="22"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
     </row>
     <row r="4" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="29"/>
@@ -4855,52 +5025,52 @@
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="20"/>
-      <c r="AE4" s="20"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="20"/>
-      <c r="AH4" s="20"/>
-      <c r="AI4" s="20"/>
-      <c r="AJ4" s="21"/>
-      <c r="AK4" s="21"/>
-      <c r="AL4" s="21"/>
-      <c r="AM4" s="21"/>
-      <c r="AN4" s="21"/>
-      <c r="AO4" s="22"/>
-      <c r="AP4" s="22"/>
-      <c r="AQ4" s="22"/>
-      <c r="AR4" s="22"/>
-      <c r="AS4" s="22"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-      <c r="AY4" s="24"/>
-      <c r="AZ4" s="24"/>
-      <c r="BA4" s="24"/>
-      <c r="BB4" s="24"/>
-      <c r="BC4" s="24"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="21"/>
+      <c r="AG4" s="21"/>
+      <c r="AH4" s="21"/>
+      <c r="AI4" s="21"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
     </row>
     <row r="6" spans="1:55" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
@@ -4909,40 +5079,40 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="25" t="str">
-        <f>レビュー前セルフチェック記録表_Task.●●!E6</f>
+      <c r="E6" s="8" t="str">
+        <f>レビュー前セルフチェック記録表_Task.25!E6</f>
         <v>AttendanceController.java
 AttendanceServise.java
 AttendanceMapper.XML</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
       <c r="O6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="8" t="str">
-        <f>レビュー前セルフチェック記録表_Task.●●!S6</f>
+      <c r="S6" s="9" t="str">
+        <f>レビュー前セルフチェック記録表_Task.25!S6</f>
         <v>Task.25,未入力勤怠確認画面の新作成</v>
       </c>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
       <c r="AC6" s="6" t="s">
         <v>37</v>
       </c>
@@ -4951,7 +5121,9 @@
       <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
-      <c r="AI6" s="26"/>
+      <c r="AI6" s="26">
+        <v>45922</v>
+      </c>
       <c r="AJ6" s="26"/>
       <c r="AK6" s="26"/>
       <c r="AL6" s="26"/>
@@ -4965,7 +5137,7 @@
       <c r="AR6" s="6"/>
       <c r="AS6" s="6"/>
       <c r="AT6" s="26" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="AU6" s="26"/>
       <c r="AV6" s="26"/>
@@ -4984,30 +5156,30 @@
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
       <c r="AC7" s="6" t="s">
         <v>40</v>
       </c>
@@ -5016,7 +5188,9 @@
       <c r="AF7" s="6"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
-      <c r="AI7" s="27"/>
+      <c r="AI7" s="27">
+        <v>0.61111111111111105</v>
+      </c>
       <c r="AJ7" s="27"/>
       <c r="AK7" s="27"/>
       <c r="AL7" s="27"/>
@@ -5030,7 +5204,7 @@
       <c r="AR7" s="6"/>
       <c r="AS7" s="6"/>
       <c r="AT7" s="27" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="AU7" s="27"/>
       <c r="AV7" s="27"/>
@@ -5047,30 +5221,30 @@
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
       <c r="AC8" s="6" t="s">
         <v>42</v>
       </c>
@@ -5079,7 +5253,9 @@
       <c r="AF8" s="6"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
-      <c r="AI8" s="27"/>
+      <c r="AI8" s="27">
+        <v>0.63888888888888895</v>
+      </c>
       <c r="AJ8" s="27"/>
       <c r="AK8" s="27"/>
       <c r="AL8" s="27"/>
@@ -5092,7 +5268,9 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
       <c r="AS8" s="6"/>
-      <c r="AT8" s="27"/>
+      <c r="AT8" s="27" t="s">
+        <v>67</v>
+      </c>
       <c r="AU8" s="27"/>
       <c r="AV8" s="27"/>
       <c r="AW8" s="27"/>
@@ -5179,7 +5357,9 @@
         <v>1</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -5188,7 +5368,9 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -5200,7 +5382,9 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
+      <c r="X10" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
@@ -5212,7 +5396,9 @@
       <c r="AG10" s="2"/>
       <c r="AH10" s="2"/>
       <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
+      <c r="AJ10" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="AK10" s="2"/>
       <c r="AL10" s="2"/>
       <c r="AM10" s="2"/>
@@ -5466,7 +5652,9 @@
         <v>2</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -5475,7 +5663,9 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -5487,7 +5677,9 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
+      <c r="X15" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
@@ -5499,7 +5691,9 @@
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
+      <c r="AJ15" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="AK15" s="2"/>
       <c r="AL15" s="2"/>
       <c r="AM15" s="2"/>
@@ -5753,7 +5947,9 @@
         <v>3</v>
       </c>
       <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -5762,7 +5958,9 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5774,7 +5972,9 @@
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
+      <c r="X20" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
@@ -5786,7 +5986,9 @@
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
+      <c r="AJ20" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
